--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -3271,7 +3271,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -8174,7 +8174,7 @@
           <t>D | 842呎 (3房)
 $2580万
 $30,641/呎
-(26年-08月-22日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -1948,38 +1948,30 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>31829</v>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K21" s="5" t="n">
+        <v>26800000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>31829</v>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
@@ -1988,7 +1980,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -7726,7 +7718,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -7736,7 +7728,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -7977,12 +7969,12 @@
 (25年-08月-26日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 842呎 (3房)
-招标单位
--
-(在售)</t>
+$2680万
+$31,829/呎
+(26年-10月-13日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr"/>

--- a/files/九龙-何文田-128 Waterloo.xlsx
+++ b/files/九龙-何文田-128 Waterloo.xlsx
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>3361</v>
+        <v>3445</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
         <v>241150000</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>71749</v>
+        <v>70000</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>241150000</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>71749</v>
+        <v>70000</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1254,7 +1254,7 @@
         <v>25626000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>44336</v>
+        <v>44259</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>25626000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>44336</v>
+        <v>44259</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         <v>69511000</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>55299</v>
+        <v>55255</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         <v>69511000</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>55299</v>
+        <v>55255</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         <v>69511000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>129927</v>
+        <v>130170</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>69511000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>129927</v>
+        <v>130170</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>19542000</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>33810</v>
+        <v>33751</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>19542000</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>33810</v>
+        <v>33751</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2146,7 +2146,7 @@
         <v>23715000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>41029</v>
+        <v>40959</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>23715000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>41029</v>
+        <v>40959</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>45695000</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>36352</v>
+        <v>36324</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>45695000</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>36352</v>
+        <v>36324</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
         <v>24126000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>45095</v>
+        <v>45180</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>24126000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>45095</v>
+        <v>45180</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>23024000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>39834</v>
+        <v>39765</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>23024000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>39834</v>
+        <v>39765</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>23652000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>44209</v>
+        <v>44292</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>23652000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>44209</v>
+        <v>44292</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>22200000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>38408</v>
+        <v>38342</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>22200000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>38408</v>
+        <v>38342</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         <v>34750000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>27645</v>
+        <v>27623</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>34750000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>27645</v>
+        <v>27623</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>22766000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>42553</v>
+        <v>42633</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>22766000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>42553</v>
+        <v>42633</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>19702000</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>34087</v>
+        <v>34028</v>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>19702000</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>34087</v>
+        <v>34028</v>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>35071000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>27901</v>
+        <v>27878</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
         <v>35071000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>27901</v>
+        <v>27878</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>19000000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>35514</v>
+        <v>35581</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>19000000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>35514</v>
+        <v>35581</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>33683000</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>26796</v>
+        <v>26775</v>
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>33683000</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>26796</v>
+        <v>26775</v>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>16337000</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>28265</v>
+        <v>28216</v>
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
@@ -4343,7 +4343,7 @@
         <v>16337000</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>28265</v>
+        <v>28216</v>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4394,7 +4394,7 @@
         <v>33600000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>26730</v>
+        <v>26709</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
         <v>33600000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>26730</v>
+        <v>26709</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
         <v>18174000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>33970</v>
+        <v>34034</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
         <v>18174000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>33970</v>
+        <v>34034</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4766,7 +4766,7 @@
         <v>17137000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>29649</v>
+        <v>29598</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4777,7 +4777,7 @@
         <v>17137000</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>29649</v>
+        <v>29598</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>33000000</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>26253</v>
+        <v>26232</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>33000000</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>26253</v>
+        <v>26232</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>18207000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>34032</v>
+        <v>34096</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>18207000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>34032</v>
+        <v>34096</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>35000000</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>27844</v>
+        <v>27822</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>35000000</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>27844</v>
+        <v>27822</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>16228000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>30333</v>
+        <v>30390</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>16228000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>30333</v>
+        <v>30390</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>30500000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>24264</v>
+        <v>24245</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5707,7 +5707,7 @@
         <v>30500000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>24264</v>
+        <v>24245</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>17330000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>32393</v>
+        <v>32453</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5769,7 +5769,7 @@
         <v>17330000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>32393</v>
+        <v>32453</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="E84" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>9947000</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>29961</v>
+        <v>30051</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>9947000</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>29961</v>
+        <v>30051</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>15317000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>26500</v>
+        <v>26454</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
         <v>15317000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>26500</v>
+        <v>26454</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
         <v>34000000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>27049</v>
+        <v>27027</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>34000000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>27049</v>
+        <v>27027</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6238,7 +6238,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6254,7 +6254,7 @@
         <v>16016000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>29936</v>
+        <v>29993</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>16016000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>29936</v>
+        <v>29993</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>9657000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>29087</v>
+        <v>29175</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>9657000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>29087</v>
+        <v>29175</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         </is>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
@@ -6688,7 +6688,7 @@
         <v>29500000</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>23469</v>
+        <v>23450</v>
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>29500000</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>23469</v>
+        <v>23450</v>
       </c>
       <c r="M97" s="3" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>16611000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>31049</v>
+        <v>31107</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>16611000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>31049</v>
+        <v>31107</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>10282000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>30970</v>
+        <v>31063</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>10282000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>30970</v>
+        <v>31063</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="E104" s="4" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         <v>14026000</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>24266</v>
+        <v>24225</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>14026000</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>24266</v>
+        <v>24225</v>
       </c>
       <c r="M104" s="3" t="inlineStr">
         <is>
@@ -7168,7 +7168,7 @@
         </is>
       </c>
       <c r="E105" s="4" t="n">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>33000000</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>26253</v>
+        <v>26232</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>33000000</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>26253</v>
+        <v>26232</v>
       </c>
       <c r="M105" s="3" t="inlineStr">
         <is>
@@ -7797,9 +7797,9 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 3361呎 (4+房)
+          <t>A | 3445呎 (4+房)
 $24115万
-$71,749/呎
+$70,000/呎
 (22年-07月-14日)</t>
         </is>
       </c>
@@ -7819,9 +7819,9 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $2563万
-$44,336/呎
+$44,259/呎
 (25年-04月-23日)</t>
         </is>
       </c>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t>G | 535呎 (null房)
+          <t>G | 534呎 (null房)
 -
 -
 (待售)</t>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="I6" s="23" t="inlineStr">
         <is>
-          <t>H | 1257呎 (null房)
+          <t>H | 1258呎 (null房)
 -
 -
 (待售)</t>
@@ -7883,9 +7883,9 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1954万
-$33,810/呎
+$33,751/呎
 (25年-08月-12日)</t>
         </is>
       </c>
@@ -7924,17 +7924,17 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (null房)
+          <t>G | 534呎 (null房)
 $6951万
-$129,927/呎
+$130,170/呎
 (26年-02月-27日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (null房)
+          <t>H | 1258呎 (null房)
 $6951万
-$55,299/呎
+$55,255/呎
 (26年-02月-27日)</t>
         </is>
       </c>
@@ -7947,9 +7947,9 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $2372万
-$41,029/呎
+$40,959/呎
 (25年-04月-29日)</t>
         </is>
       </c>
@@ -8011,9 +8011,9 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $2302万
-$39,834/呎
+$39,765/呎
 (24年-09月-05日)</t>
         </is>
       </c>
@@ -8052,17 +8052,17 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $2413万
-$45,095/呎
+$45,180/呎
 (24年-08月-01日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $4570万
-$36,352/呎
+$36,324/呎
 (25年-03月-11日)</t>
         </is>
       </c>
@@ -8075,9 +8075,9 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $2220万
-$38,408/呎
+$38,342/呎
 (24年-06月-17日)</t>
         </is>
       </c>
@@ -8116,15 +8116,15 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $2365万
-$44,209/呎
+$44,292/呎
 (24年-06月-25日)</t>
         </is>
       </c>
       <c r="I10" s="24" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 -
 -
 (暂停销售)</t>
@@ -8139,9 +8139,9 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1970万
-$34,087/呎
+$34,028/呎
 (24年-06月-05日)</t>
         </is>
       </c>
@@ -8180,17 +8180,17 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $2277万
-$42,553/呎
+$42,633/呎
 (24年-07月-04日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3475万
-$27,645/呎
+$27,623/呎
 (23年-02月-28日)</t>
         </is>
       </c>
@@ -8244,17 +8244,17 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1900万
-$35,514/呎
+$35,581/呎
 (23年-04月-18日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3507万
-$27,901/呎
+$27,878/呎
 (23年-02月-02日)</t>
         </is>
       </c>
@@ -8267,9 +8267,9 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1634万
-$28,265/呎
+$28,216/呎
 (23年-10月-11日)</t>
         </is>
       </c>
@@ -8316,9 +8316,9 @@
       </c>
       <c r="I13" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3368万
-$26,796/呎
+$26,775/呎
 (23年-03月-17日)</t>
         </is>
       </c>
@@ -8331,9 +8331,9 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1714万
-$29,649/呎
+$29,598/呎
 (23年-03月-21日)</t>
         </is>
       </c>
@@ -8372,17 +8372,17 @@
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1817万
-$33,970/呎
+$34,034/呎
 (23年-07月-18日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3360万
-$26,730/呎
+$26,709/呎
 (23年-02月-06日)</t>
         </is>
       </c>
@@ -8436,17 +8436,17 @@
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1821万
-$34,032/呎
+$34,096/呎
 (22年-01月-13日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3300万
-$26,253/呎
+$26,232/呎
 (23年-06月-13日)</t>
         </is>
       </c>
@@ -8500,17 +8500,17 @@
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1623万
-$30,333/呎
+$30,390/呎
 (21年-05月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3500万
-$27,844/呎
+$27,822/呎
 (25年-11月-20日)</t>
         </is>
       </c>
@@ -8523,9 +8523,9 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1532万
-$26,500/呎
+$26,454/呎
 (24年-05月-02日)</t>
         </is>
       </c>
@@ -8555,9 +8555,9 @@
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>E | 332呎 (1房)
+          <t>E | 331呎 (1房)
 $995万
-$29,961/呎
+$30,051/呎
 (20年-11月-05日)</t>
         </is>
       </c>
@@ -8571,17 +8571,17 @@
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1733万
-$32,393/呎
+$32,453/呎
 (21年-12月-31日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3050万
-$24,264/呎
+$24,245/呎
 (23年-01月-10日)</t>
         </is>
       </c>
@@ -8626,9 +8626,9 @@
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>E | 332呎 (1房)
+          <t>E | 331呎 (1房)
 $966万
-$29,087/呎
+$29,175/呎
 (21年-05月-25日)</t>
         </is>
       </c>
@@ -8642,17 +8642,17 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1602万
-$29,936/呎
+$29,993/呎
 (20年-11月-03日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3400万
-$27,049/呎
+$27,027/呎
 (22年-11月-01日)</t>
         </is>
       </c>
@@ -8665,9 +8665,9 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>A | 578呎 (2房)
+          <t>A | 579呎 (2房)
 $1403万
-$24,266/呎
+$24,225/呎
 (21年-04月-09日)</t>
         </is>
       </c>
@@ -8697,9 +8697,9 @@
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>E | 332呎 (1房)
+          <t>E | 331呎 (1房)
 $1028万
-$30,970/呎
+$31,063/呎
 (21年-08月-27日)</t>
         </is>
       </c>
@@ -8713,17 +8713,17 @@
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>G | 535呎 (2房)
+          <t>G | 534呎 (2房)
 $1661万
-$31,049/呎
+$31,107/呎
 (23年-02月-20日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $2950万
-$23,469/呎
+$23,450/呎
 (23年-02月-08日)</t>
         </is>
       </c>
@@ -8792,9 +8792,9 @@
       </c>
       <c r="I20" s="20" t="inlineStr">
         <is>
-          <t>H | 1257呎 (4+房)
+          <t>H | 1258呎 (4+房)
 $3300万
-$26,253/呎
+$26,232/呎
 (22年-11月-01日)</t>
         </is>
       </c>
